--- a/artfynd/Gålggåmisvárre artfynd.xlsx
+++ b/artfynd/Gålggåmisvárre artfynd.xlsx
@@ -14785,6 +14785,9 @@
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
+      <c r="J129" t="inlineStr"/>
+      <c r="K129" t="inlineStr"/>
+      <c r="N129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
           <t>Gålggåmisvárre, Pi lm</t>
@@ -14841,7 +14844,7 @@
       </c>
       <c r="AC129" t="inlineStr">
         <is>
-          <t>Fruktkroppar från i fjol</t>
+          <t>Fruktkroppar från i fjol. Torr tallskog, kuperad sandig grusig morän.</t>
         </is>
       </c>
       <c r="AD129" t="b">

--- a/artfynd/Gålggåmisvárre artfynd.xlsx
+++ b/artfynd/Gålggåmisvárre artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY297"/>
+  <dimension ref="A1:AZ297"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -788,6 +793,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294829</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -904,6 +914,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135301776</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1015,6 +1030,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294818</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1126,6 +1146,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294827</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1237,6 +1262,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294830</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1348,6 +1378,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294834</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1463,6 +1498,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294832</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1574,6 +1614,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294841</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1685,6 +1730,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294826</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1796,6 +1846,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294833</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1907,6 +1962,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294828</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2018,6 +2078,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294831</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2115,6 +2180,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123975</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2230,6 +2300,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135295377</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2365,6 +2440,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294352</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2462,6 +2542,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120413487</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2607,6 +2692,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294350</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2714,6 +2804,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294354</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2821,6 +2916,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294364</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2932,6 +3032,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294783</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3043,6 +3148,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294791</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3154,6 +3264,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294837</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3265,6 +3380,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294850</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3376,6 +3496,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294854</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3487,6 +3612,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135295381</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3598,6 +3728,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135295383</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3709,6 +3844,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135298434</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3820,6 +3960,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135300485</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3931,6 +4076,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135300494</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4042,6 +4192,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135300500</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4158,6 +4313,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135300572</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4269,6 +4429,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135301725</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4380,6 +4545,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135301737</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4491,6 +4661,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135301777</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4602,6 +4777,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135301793</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4713,6 +4893,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294795</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4824,6 +5009,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135301800</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4921,6 +5111,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/473616</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5048,6 +5243,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294361</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5159,6 +5359,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135295390</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5266,6 +5471,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135298393</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5373,6 +5583,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135298394</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5480,6 +5695,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135298401</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5591,6 +5811,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135300576</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5688,6 +5913,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120403743</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5785,6 +6015,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120413471</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5896,6 +6131,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294851</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5993,6 +6233,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120413476</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6100,6 +6345,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294365</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6211,6 +6461,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135300496</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6322,6 +6577,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135301730</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6429,6 +6689,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294359</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6536,6 +6801,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294363</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6647,6 +6917,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294852</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6763,6 +7038,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135301781</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6860,6 +7140,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120413475</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6971,6 +7256,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135301740</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -7113,6 +7403,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294351</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -7224,6 +7519,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135300495</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7335,6 +7635,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135301732</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7446,6 +7751,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135301797</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7553,6 +7863,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294358</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7664,6 +7979,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294797</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7771,6 +8091,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135298397</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7886,6 +8211,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135298398</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7997,6 +8327,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135298433</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -8108,6 +8443,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135300487</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -8205,6 +8545,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120413482</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -8316,6 +8661,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135295380</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -8413,6 +8763,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120413467</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8524,6 +8879,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294782</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8635,6 +8995,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294784</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8746,6 +9111,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294787</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8857,6 +9227,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294788</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8968,6 +9343,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294790</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -9079,6 +9459,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294794</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -9190,6 +9575,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294836</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -9301,6 +9691,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294847</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -9412,6 +9807,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294849</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -9523,6 +9923,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135295388</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -9630,6 +10035,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135298391</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9741,6 +10151,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135298435</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9852,6 +10267,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135300492</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9963,6 +10383,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135301733</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -10074,6 +10499,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135301780</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -10185,6 +10615,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135301783</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -10296,6 +10731,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294793</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -10413,6 +10853,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294360</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -10533,6 +10978,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294378</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -10649,6 +11099,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294789</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -10760,6 +11215,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135298432</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -10876,6 +11336,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135300490</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -10992,6 +11457,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135301804</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -11108,6 +11578,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135301738</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -11224,6 +11699,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135301803</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -11331,6 +11811,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294357</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -11442,6 +11927,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294781</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -11551,6 +12041,11 @@
       <c r="AY99" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294843</t>
         </is>
       </c>
     </row>
@@ -11669,6 +12164,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135295389</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -11780,6 +12280,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135300497</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -11891,6 +12396,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135301728</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -12002,6 +12512,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135301791</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -12113,6 +12628,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135295379</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -12224,6 +12744,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135300488</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -12335,6 +12860,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135300493</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -12446,6 +12976,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135301778</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -12557,6 +13092,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135301796</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -12664,6 +13204,11 @@
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294355</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -12775,6 +13320,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294785</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -12886,6 +13436,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135295378</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -12997,6 +13552,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135295386</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -13108,6 +13668,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135295387</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -13215,6 +13780,11 @@
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135298403</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -13326,6 +13896,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135300489</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -13437,6 +14012,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135300491</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -13548,6 +14128,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135300574</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -13659,6 +14244,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135300575</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -13770,6 +14360,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135301794</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -13877,6 +14472,11 @@
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135291042</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -13984,6 +14584,11 @@
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294356</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -14091,6 +14696,11 @@
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294362</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -14202,6 +14812,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ123" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294796</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -14313,6 +14928,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294853</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -14424,6 +15044,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135295384</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -14536,6 +15161,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135295385</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -14647,6 +15277,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135301727</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -14756,6 +15391,11 @@
       <c r="AY128" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ128" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135301735</t>
         </is>
       </c>
     </row>
@@ -14873,6 +15513,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ129" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135295442</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -14980,6 +15625,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ130" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135301801</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -15091,6 +15741,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ131" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135300502</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -15188,6 +15843,11 @@
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
+      <c r="AZ132" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120403757</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -15285,6 +15945,11 @@
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
+      <c r="AZ133" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120403759</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -15382,6 +16047,11 @@
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
+      <c r="AZ134" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120413485</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -15479,6 +16149,11 @@
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
+      <c r="AZ135" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120413486</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -15586,6 +16261,11 @@
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
+      <c r="AZ136" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294374</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -15697,6 +16377,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ137" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294800</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -15808,6 +16493,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ138" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294823</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -15919,6 +16609,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ139" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294824</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -16030,6 +16725,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ140" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135298439</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -16141,6 +16841,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ141" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135298457</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -16252,6 +16957,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ142" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135298458</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -16363,6 +17073,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ143" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135300504</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -16479,6 +17194,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ144" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135300508</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -16595,6 +17315,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ145" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135300511</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -16706,6 +17431,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ146" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135300526</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -16817,6 +17547,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ147" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135300531</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -16933,6 +17668,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ148" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135300534</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -17044,6 +17784,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ149" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135300537</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -17155,6 +17900,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ150" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135300541</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -17266,6 +18016,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ151" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135300552</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -17377,6 +18132,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ152" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135300555</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -17488,6 +18248,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ153" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135300560</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -17599,6 +18364,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ154" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135300561</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -17715,6 +18485,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ155" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135300562</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -17826,6 +18601,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ156" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135300568</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -17937,6 +18717,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ157" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135300569</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -18048,6 +18833,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ158" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135301768</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -18159,6 +18949,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ159" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294811</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -18270,6 +19065,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ160" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135300523</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -18382,6 +19182,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ161" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135301784</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -18493,6 +19298,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ162" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135300510</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -18590,6 +19400,11 @@
         </is>
       </c>
       <c r="AY163" t="inlineStr"/>
+      <c r="AZ163" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120403756</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -18701,6 +19516,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ164" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135298436</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -18812,6 +19632,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ165" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135298437</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -18923,6 +19748,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ166" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135300514</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -19034,6 +19864,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ167" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135300540</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
@@ -19145,6 +19980,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ168" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135300566</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
@@ -19242,6 +20082,11 @@
         </is>
       </c>
       <c r="AY169" t="inlineStr"/>
+      <c r="AZ169" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120403740</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
@@ -19339,6 +20184,11 @@
         </is>
       </c>
       <c r="AY170" t="inlineStr"/>
+      <c r="AZ170" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120403742</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -19436,6 +20286,11 @@
         </is>
       </c>
       <c r="AY171" t="inlineStr"/>
+      <c r="AZ171" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120413470</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
@@ -19547,6 +20402,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ172" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135300513</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
@@ -19658,6 +20518,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ173" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135300516</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
@@ -19769,6 +20634,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ174" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135300519</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
@@ -19866,6 +20736,11 @@
         </is>
       </c>
       <c r="AY175" t="inlineStr"/>
+      <c r="AZ175" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120403734</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
@@ -19977,6 +20852,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ176" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135300542</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
@@ -20088,6 +20968,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ177" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294839</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
@@ -20199,6 +21084,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ178" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135298447</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
@@ -20315,6 +21205,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ179" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135301769</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
@@ -20412,6 +21307,11 @@
         </is>
       </c>
       <c r="AY180" t="inlineStr"/>
+      <c r="AZ180" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120403745</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
@@ -20523,6 +21423,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ181" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135300520</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
@@ -20620,6 +21525,11 @@
         </is>
       </c>
       <c r="AY182" t="inlineStr"/>
+      <c r="AZ182" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120413494</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
@@ -20717,6 +21627,11 @@
         </is>
       </c>
       <c r="AY183" t="inlineStr"/>
+      <c r="AZ183" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120413495</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
@@ -20828,6 +21743,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ184" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135300509</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
@@ -20939,6 +21859,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ185" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135300525</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
@@ -21050,6 +21975,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ186" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135300529</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
@@ -21147,6 +22077,11 @@
         </is>
       </c>
       <c r="AY187" t="inlineStr"/>
+      <c r="AZ187" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120403751</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
@@ -21244,6 +22179,11 @@
         </is>
       </c>
       <c r="AY188" t="inlineStr"/>
+      <c r="AZ188" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120403753</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
@@ -21341,6 +22281,11 @@
         </is>
       </c>
       <c r="AY189" t="inlineStr"/>
+      <c r="AZ189" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120403754</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
@@ -21438,6 +22383,11 @@
         </is>
       </c>
       <c r="AY190" t="inlineStr"/>
+      <c r="AZ190" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120403755</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
@@ -21535,6 +22485,11 @@
         </is>
       </c>
       <c r="AY191" t="inlineStr"/>
+      <c r="AZ191" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120413479</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
@@ -21632,6 +22587,11 @@
         </is>
       </c>
       <c r="AY192" t="inlineStr"/>
+      <c r="AZ192" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120413480</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
@@ -21729,6 +22689,11 @@
         </is>
       </c>
       <c r="AY193" t="inlineStr"/>
+      <c r="AZ193" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120413481</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
@@ -21840,6 +22805,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ194" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294821</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
@@ -21951,6 +22921,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ195" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135298443</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
@@ -22062,6 +23037,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ196" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135300507</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
@@ -22173,6 +23153,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ197" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135300515</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
@@ -22284,6 +23269,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ198" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135300521</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
@@ -22395,6 +23385,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ199" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135301762</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
@@ -22492,6 +23487,11 @@
         </is>
       </c>
       <c r="AY200" t="inlineStr"/>
+      <c r="AZ200" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120403737</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
@@ -22589,6 +23589,11 @@
         </is>
       </c>
       <c r="AY201" t="inlineStr"/>
+      <c r="AZ201" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120403738</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
@@ -22686,6 +23691,11 @@
         </is>
       </c>
       <c r="AY202" t="inlineStr"/>
+      <c r="AZ202" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120413464</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
@@ -22783,6 +23793,11 @@
         </is>
       </c>
       <c r="AY203" t="inlineStr"/>
+      <c r="AZ203" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120413465</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
@@ -22890,6 +23905,11 @@
         </is>
       </c>
       <c r="AY204" t="inlineStr"/>
+      <c r="AZ204" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294373</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
@@ -22997,6 +24017,11 @@
         </is>
       </c>
       <c r="AY205" t="inlineStr"/>
+      <c r="AZ205" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294375</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
@@ -23108,6 +24133,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ206" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294799</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
@@ -23219,6 +24249,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ207" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294813</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
@@ -23330,6 +24365,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ208" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294820</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
@@ -23441,6 +24481,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ209" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294840</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="n">
@@ -23552,6 +24597,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ210" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135298459</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
@@ -23663,6 +24713,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ211" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135300498</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="n">
@@ -23774,6 +24829,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ212" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135300503</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="n">
@@ -23885,6 +24945,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ213" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135300517</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="n">
@@ -23996,6 +25061,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ214" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135300530</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="n">
@@ -24107,6 +25177,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ215" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135300532</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="n">
@@ -24218,6 +25293,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ216" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135300536</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="n">
@@ -24329,6 +25409,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ217" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135300547</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="n">
@@ -24440,6 +25525,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ218" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135300548</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="n">
@@ -24551,6 +25641,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ219" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135300551</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="n">
@@ -24662,6 +25757,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ220" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135300565</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="n">
@@ -24773,6 +25873,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ221" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135301743</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="n">
@@ -24884,6 +25989,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ222" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135301764</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="n">
@@ -24995,6 +26105,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ223" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135301774</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="n">
@@ -25106,6 +26221,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ224" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135301786</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="n">
@@ -25217,6 +26337,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ225" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135301788</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="n">
@@ -25328,6 +26453,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ226" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135300544</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="n">
@@ -25439,6 +26569,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ227" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135300545</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="n">
@@ -25536,6 +26671,11 @@
         </is>
       </c>
       <c r="AY228" t="inlineStr"/>
+      <c r="AZ228" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120413473</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="n">
@@ -25633,6 +26773,11 @@
         </is>
       </c>
       <c r="AY229" t="inlineStr"/>
+      <c r="AZ229" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120413474</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="n">
@@ -25744,6 +26889,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ230" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294807</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="n">
@@ -25855,6 +27005,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ231" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294815</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="n">
@@ -25966,6 +27121,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ232" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135301748</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="n">
@@ -26063,6 +27223,11 @@
         </is>
       </c>
       <c r="AY233" t="inlineStr"/>
+      <c r="AZ233" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120413490</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="n">
@@ -26160,6 +27325,11 @@
         </is>
       </c>
       <c r="AY234" t="inlineStr"/>
+      <c r="AZ234" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120413491</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="n">
@@ -26271,6 +27441,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ235" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294805</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="n">
@@ -26382,6 +27557,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ236" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135301749</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="n">
@@ -26493,6 +27673,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ237" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135301754</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="n">
@@ -26590,6 +27775,11 @@
         </is>
       </c>
       <c r="AY238" t="inlineStr"/>
+      <c r="AZ238" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120413477</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="n">
@@ -26701,6 +27891,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ239" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135301751</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="n">
@@ -26798,6 +27993,11 @@
         </is>
       </c>
       <c r="AY240" t="inlineStr"/>
+      <c r="AZ240" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120413492</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="n">
@@ -26895,6 +28095,11 @@
         </is>
       </c>
       <c r="AY241" t="inlineStr"/>
+      <c r="AZ241" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120413493</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="n">
@@ -27006,6 +28211,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ242" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135300527</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="n">
@@ -27117,6 +28327,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ243" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294809</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="n">
@@ -27233,6 +28448,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ244" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135300506</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="n">
@@ -27349,6 +28569,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ245" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135300543</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="n">
@@ -27451,6 +28676,11 @@
         </is>
       </c>
       <c r="AY246" t="inlineStr"/>
+      <c r="AZ246" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120403746</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="n">
@@ -27567,6 +28797,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ247" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294810</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="n">
@@ -27691,6 +28926,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ248" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135298406</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="n">
@@ -27802,6 +29042,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ249" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135298438</t>
+        </is>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="n">
@@ -27918,6 +29163,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ250" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135298440</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="n">
@@ -28034,6 +29284,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ251" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135298445</t>
+        </is>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="n">
@@ -28150,6 +29405,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ252" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135300553</t>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="n">
@@ -28266,6 +29526,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ253" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135300563</t>
+        </is>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="n">
@@ -28382,6 +29647,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ254" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135300567</t>
+        </is>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="n">
@@ -28479,6 +29749,11 @@
         </is>
       </c>
       <c r="AY255" t="inlineStr"/>
+      <c r="AZ255" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120413472</t>
+        </is>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="n">
@@ -28590,6 +29865,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ256" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135301755</t>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="n">
@@ -28706,6 +29986,11 @@
         </is>
       </c>
       <c r="AY257" t="inlineStr"/>
+      <c r="AZ257" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294377</t>
+        </is>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="n">
@@ -28826,6 +30111,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ258" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135300538</t>
+        </is>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="n">
@@ -28937,6 +30227,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ259" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135300501</t>
+        </is>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="n">
@@ -29048,6 +30343,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ260" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135301756</t>
+        </is>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="n">
@@ -29159,6 +30459,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ261" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294816</t>
+        </is>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="n">
@@ -29270,6 +30575,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ262" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135301744</t>
+        </is>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="n">
@@ -29381,6 +30691,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ263" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294825</t>
+        </is>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="n">
@@ -29492,6 +30807,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ264" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135301741</t>
+        </is>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="n">
@@ -29603,6 +30923,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ265" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135301757</t>
+        </is>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="n">
@@ -29714,6 +31039,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ266" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135301766</t>
+        </is>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="n">
@@ -29825,6 +31155,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ267" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135301770</t>
+        </is>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="n">
@@ -29936,6 +31271,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ268" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135301790</t>
+        </is>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="n">
@@ -30047,6 +31387,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ269" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135298442</t>
+        </is>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="n">
@@ -30158,6 +31503,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ270" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135301747</t>
+        </is>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="n">
@@ -30269,6 +31619,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ271" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135301759</t>
+        </is>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="n">
@@ -30380,6 +31735,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ272" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135295146</t>
+        </is>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="n">
@@ -30477,6 +31837,11 @@
         </is>
       </c>
       <c r="AY273" t="inlineStr"/>
+      <c r="AZ273" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120403747</t>
+        </is>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="n">
@@ -30574,6 +31939,11 @@
         </is>
       </c>
       <c r="AY274" t="inlineStr"/>
+      <c r="AZ274" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120403748</t>
+        </is>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="n">
@@ -30685,6 +32055,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ275" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135298444</t>
+        </is>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="n">
@@ -30796,6 +32171,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ276" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135298446</t>
+        </is>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="n">
@@ -30907,6 +32287,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ277" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135300550</t>
+        </is>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="n">
@@ -31018,6 +32403,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ278" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135301752</t>
+        </is>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="n">
@@ -31115,6 +32505,11 @@
         </is>
       </c>
       <c r="AY279" t="inlineStr"/>
+      <c r="AZ279" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120413469</t>
+        </is>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="n">
@@ -31226,6 +32621,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ280" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294801</t>
+        </is>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="n">
@@ -31337,6 +32737,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ281" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294812</t>
+        </is>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="n">
@@ -31444,6 +32849,11 @@
         </is>
       </c>
       <c r="AY282" t="inlineStr"/>
+      <c r="AZ282" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135298407</t>
+        </is>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="n">
@@ -31555,6 +32965,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ283" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135300524</t>
+        </is>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="n">
@@ -31666,6 +33081,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ284" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135300528</t>
+        </is>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="n">
@@ -31777,6 +33197,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ285" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135300533</t>
+        </is>
+      </c>
     </row>
     <row r="286">
       <c r="A286" t="n">
@@ -31888,6 +33313,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ286" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135300539</t>
+        </is>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="n">
@@ -31999,6 +33429,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ287" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135300546</t>
+        </is>
+      </c>
     </row>
     <row r="288">
       <c r="A288" t="n">
@@ -32110,6 +33545,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ288" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135300549</t>
+        </is>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="n">
@@ -32221,6 +33661,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ289" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135300554</t>
+        </is>
+      </c>
     </row>
     <row r="290">
       <c r="A290" t="n">
@@ -32332,6 +33777,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ290" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135300557</t>
+        </is>
+      </c>
     </row>
     <row r="291">
       <c r="A291" t="n">
@@ -32443,6 +33893,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ291" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135300564</t>
+        </is>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="n">
@@ -32554,6 +34009,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ292" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135301787</t>
+        </is>
+      </c>
     </row>
     <row r="293">
       <c r="A293" t="n">
@@ -32661,6 +34121,11 @@
         </is>
       </c>
       <c r="AY293" t="inlineStr"/>
+      <c r="AZ293" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294376</t>
+        </is>
+      </c>
     </row>
     <row r="294">
       <c r="A294" t="n">
@@ -32772,6 +34237,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ294" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294835</t>
+        </is>
+      </c>
     </row>
     <row r="295">
       <c r="A295" t="n">
@@ -32888,6 +34358,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ295" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135300505</t>
+        </is>
+      </c>
     </row>
     <row r="296">
       <c r="A296" t="n">
@@ -32999,6 +34474,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ296" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135301765</t>
+        </is>
+      </c>
     </row>
     <row r="297">
       <c r="A297" t="n">
@@ -33110,8 +34590,311 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ297" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135301773</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ131" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ132" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ133" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ134" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ135" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ136" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ137" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ138" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ139" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ140" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ141" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ142" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ143" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ144" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ145" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ146" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ147" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ148" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ149" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ150" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ151" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ152" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ153" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ154" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ155" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ156" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ157" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ158" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ159" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ160" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ161" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ162" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ163" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ164" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ165" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ166" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ167" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ168" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ169" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ170" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ171" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ172" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ173" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ174" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ175" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ176" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ177" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ178" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ179" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ180" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ181" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ182" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ183" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ184" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ185" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ186" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ187" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ188" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ189" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ190" r:id="rId189"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ191" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ192" r:id="rId191"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ193" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ194" r:id="rId193"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ195" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ196" r:id="rId195"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ197" r:id="rId196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ198" r:id="rId197"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ199" r:id="rId198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ200" r:id="rId199"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ201" r:id="rId200"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ202" r:id="rId201"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ203" r:id="rId202"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ204" r:id="rId203"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ205" r:id="rId204"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ206" r:id="rId205"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ207" r:id="rId206"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ208" r:id="rId207"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ209" r:id="rId208"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ210" r:id="rId209"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ211" r:id="rId210"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ212" r:id="rId211"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ213" r:id="rId212"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ214" r:id="rId213"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ215" r:id="rId214"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ216" r:id="rId215"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ217" r:id="rId216"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ218" r:id="rId217"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ219" r:id="rId218"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ220" r:id="rId219"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ221" r:id="rId220"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ222" r:id="rId221"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ223" r:id="rId222"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ224" r:id="rId223"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ225" r:id="rId224"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ226" r:id="rId225"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ227" r:id="rId226"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ228" r:id="rId227"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ229" r:id="rId228"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ230" r:id="rId229"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ231" r:id="rId230"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ232" r:id="rId231"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ233" r:id="rId232"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ234" r:id="rId233"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ235" r:id="rId234"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ236" r:id="rId235"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ237" r:id="rId236"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ238" r:id="rId237"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ239" r:id="rId238"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ240" r:id="rId239"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ241" r:id="rId240"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ242" r:id="rId241"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ243" r:id="rId242"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ244" r:id="rId243"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ245" r:id="rId244"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ246" r:id="rId245"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ247" r:id="rId246"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ248" r:id="rId247"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ249" r:id="rId248"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ250" r:id="rId249"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ251" r:id="rId250"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ252" r:id="rId251"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ253" r:id="rId252"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ254" r:id="rId253"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ255" r:id="rId254"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ256" r:id="rId255"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ257" r:id="rId256"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ258" r:id="rId257"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ259" r:id="rId258"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ260" r:id="rId259"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ261" r:id="rId260"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ262" r:id="rId261"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ263" r:id="rId262"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ264" r:id="rId263"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ265" r:id="rId264"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ266" r:id="rId265"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ267" r:id="rId266"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ268" r:id="rId267"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ269" r:id="rId268"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ270" r:id="rId269"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ271" r:id="rId270"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ272" r:id="rId271"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ273" r:id="rId272"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ274" r:id="rId273"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ275" r:id="rId274"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ276" r:id="rId275"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ277" r:id="rId276"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ278" r:id="rId277"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ279" r:id="rId278"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ280" r:id="rId279"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ281" r:id="rId280"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ282" r:id="rId281"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ283" r:id="rId282"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ284" r:id="rId283"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ285" r:id="rId284"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ286" r:id="rId285"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ287" r:id="rId286"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ288" r:id="rId287"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ289" r:id="rId288"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ290" r:id="rId289"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ291" r:id="rId290"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ292" r:id="rId291"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ293" r:id="rId292"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ294" r:id="rId293"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ295" r:id="rId294"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ296" r:id="rId295"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ297" r:id="rId296"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/Gålggåmisvárre artfynd.xlsx
+++ b/artfynd/Gålggåmisvárre artfynd.xlsx
@@ -7030,7 +7030,7 @@
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Pia Edfors, Petra Wikström</t>
+          <t>Petra Wikström, Pia Edfors</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr">
@@ -10491,7 +10491,7 @@
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Pia Edfors, Petra Wikström</t>
+          <t>Petra Wikström, Pia Edfors</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr">
@@ -10607,7 +10607,7 @@
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Pia Edfors, Petra Wikström</t>
+          <t>Petra Wikström, Pia Edfors</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr">
@@ -19174,7 +19174,7 @@
       </c>
       <c r="AX161" t="inlineStr">
         <is>
-          <t>Pia Edfors, Petra Wikström</t>
+          <t>Petra Wikström, Pia Edfors</t>
         </is>
       </c>
       <c r="AY161" t="inlineStr">

--- a/artfynd/Gålggåmisvárre artfynd.xlsx
+++ b/artfynd/Gålggåmisvárre artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135294829</v>
       </c>
       <c r="B2" t="n">
-        <v>93265</v>
+        <v>93307</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>135301776</v>
       </c>
       <c r="B3" t="n">
-        <v>93271</v>
+        <v>93313</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>135294818</v>
       </c>
       <c r="B4" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1041,7 +1041,7 @@
         <v>135294827</v>
       </c>
       <c r="B5" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1157,7 +1157,7 @@
         <v>135294830</v>
       </c>
       <c r="B6" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1273,7 +1273,7 @@
         <v>135294834</v>
       </c>
       <c r="B7" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1389,7 +1389,7 @@
         <v>135294832</v>
       </c>
       <c r="B8" t="n">
-        <v>58136</v>
+        <v>58141</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1509,7 +1509,7 @@
         <v>135294841</v>
       </c>
       <c r="B9" t="n">
-        <v>98066</v>
+        <v>98110</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1625,7 +1625,7 @@
         <v>135294826</v>
       </c>
       <c r="B10" t="n">
-        <v>79963</v>
+        <v>80001</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         <v>135294833</v>
       </c>
       <c r="B11" t="n">
-        <v>79963</v>
+        <v>80001</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1857,7 +1857,7 @@
         <v>135294828</v>
       </c>
       <c r="B12" t="n">
-        <v>79396</v>
+        <v>79434</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1973,7 +1973,7 @@
         <v>135294831</v>
       </c>
       <c r="B13" t="n">
-        <v>79396</v>
+        <v>79434</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2191,7 +2191,7 @@
         <v>135295377</v>
       </c>
       <c r="B15" t="n">
-        <v>92220</v>
+        <v>92262</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2311,7 +2311,7 @@
         <v>135294352</v>
       </c>
       <c r="B16" t="n">
-        <v>92369</v>
+        <v>92411</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2553,7 +2553,7 @@
         <v>135294350</v>
       </c>
       <c r="B18" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2703,7 +2703,7 @@
         <v>135294354</v>
       </c>
       <c r="B19" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2815,7 +2815,7 @@
         <v>135294364</v>
       </c>
       <c r="B20" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2927,7 +2927,7 @@
         <v>135294783</v>
       </c>
       <c r="B21" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3043,7 +3043,7 @@
         <v>135294791</v>
       </c>
       <c r="B22" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3159,7 +3159,7 @@
         <v>135294837</v>
       </c>
       <c r="B23" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3275,7 +3275,7 @@
         <v>135294850</v>
       </c>
       <c r="B24" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3391,7 +3391,7 @@
         <v>135294854</v>
       </c>
       <c r="B25" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3507,7 +3507,7 @@
         <v>135295381</v>
       </c>
       <c r="B26" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3623,7 +3623,7 @@
         <v>135295383</v>
       </c>
       <c r="B27" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3739,7 +3739,7 @@
         <v>135298434</v>
       </c>
       <c r="B28" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3855,7 +3855,7 @@
         <v>135300485</v>
       </c>
       <c r="B29" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3971,7 +3971,7 @@
         <v>135300494</v>
       </c>
       <c r="B30" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4087,7 +4087,7 @@
         <v>135300500</v>
       </c>
       <c r="B31" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4203,7 +4203,7 @@
         <v>135300572</v>
       </c>
       <c r="B32" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4324,7 +4324,7 @@
         <v>135301725</v>
       </c>
       <c r="B33" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4440,7 +4440,7 @@
         <v>135301737</v>
       </c>
       <c r="B34" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4556,7 +4556,7 @@
         <v>135301777</v>
       </c>
       <c r="B35" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4672,7 +4672,7 @@
         <v>135301793</v>
       </c>
       <c r="B36" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4788,7 +4788,7 @@
         <v>135294795</v>
       </c>
       <c r="B37" t="n">
-        <v>79452</v>
+        <v>79490</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4904,7 +4904,7 @@
         <v>135301800</v>
       </c>
       <c r="B38" t="n">
-        <v>81355</v>
+        <v>81393</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5122,7 +5122,7 @@
         <v>135294361</v>
       </c>
       <c r="B40" t="n">
-        <v>92153</v>
+        <v>92195</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5254,7 +5254,7 @@
         <v>135295390</v>
       </c>
       <c r="B41" t="n">
-        <v>92153</v>
+        <v>92195</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5370,7 +5370,7 @@
         <v>135298393</v>
       </c>
       <c r="B42" t="n">
-        <v>92153</v>
+        <v>92195</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5482,7 +5482,7 @@
         <v>135298394</v>
       </c>
       <c r="B43" t="n">
-        <v>92153</v>
+        <v>92195</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5594,7 +5594,7 @@
         <v>135298401</v>
       </c>
       <c r="B44" t="n">
-        <v>92153</v>
+        <v>92195</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5706,7 +5706,7 @@
         <v>135300576</v>
       </c>
       <c r="B45" t="n">
-        <v>92153</v>
+        <v>92195</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6026,7 +6026,7 @@
         <v>135294851</v>
       </c>
       <c r="B48" t="n">
-        <v>90997</v>
+        <v>91039</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6244,7 +6244,7 @@
         <v>135294365</v>
       </c>
       <c r="B50" t="n">
-        <v>92027</v>
+        <v>92069</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6356,7 +6356,7 @@
         <v>135300496</v>
       </c>
       <c r="B51" t="n">
-        <v>92027</v>
+        <v>92069</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6472,7 +6472,7 @@
         <v>135301730</v>
       </c>
       <c r="B52" t="n">
-        <v>92027</v>
+        <v>92069</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6588,7 +6588,7 @@
         <v>135294359</v>
       </c>
       <c r="B53" t="n">
-        <v>91896</v>
+        <v>91938</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6700,7 +6700,7 @@
         <v>135294363</v>
       </c>
       <c r="B54" t="n">
-        <v>93271</v>
+        <v>93313</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6812,7 +6812,7 @@
         <v>135294852</v>
       </c>
       <c r="B55" t="n">
-        <v>93271</v>
+        <v>93313</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6928,7 +6928,7 @@
         <v>135301781</v>
       </c>
       <c r="B56" t="n">
-        <v>93271</v>
+        <v>93313</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7030,7 +7030,7 @@
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Petra Wikström, Pia Edfors</t>
+          <t>Pia Edfors, Petra Wikström</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr">
@@ -7151,7 +7151,7 @@
         <v>135301740</v>
       </c>
       <c r="B58" t="n">
-        <v>93275</v>
+        <v>93317</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7267,7 +7267,7 @@
         <v>135294351</v>
       </c>
       <c r="B59" t="n">
-        <v>91937</v>
+        <v>91979</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7414,7 +7414,7 @@
         <v>135300495</v>
       </c>
       <c r="B60" t="n">
-        <v>91937</v>
+        <v>91979</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7530,7 +7530,7 @@
         <v>135301732</v>
       </c>
       <c r="B61" t="n">
-        <v>91937</v>
+        <v>91979</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7646,7 +7646,7 @@
         <v>135301797</v>
       </c>
       <c r="B62" t="n">
-        <v>91937</v>
+        <v>91979</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7762,7 +7762,7 @@
         <v>135294358</v>
       </c>
       <c r="B63" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7874,7 +7874,7 @@
         <v>135294797</v>
       </c>
       <c r="B64" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7990,7 +7990,7 @@
         <v>135298397</v>
       </c>
       <c r="B65" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8102,7 +8102,7 @@
         <v>135298398</v>
       </c>
       <c r="B66" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8222,7 +8222,7 @@
         <v>135298433</v>
       </c>
       <c r="B67" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8338,7 +8338,7 @@
         <v>135300487</v>
       </c>
       <c r="B68" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8556,7 +8556,7 @@
         <v>135295380</v>
       </c>
       <c r="B70" t="n">
-        <v>79130</v>
+        <v>79168</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8774,7 +8774,7 @@
         <v>135294782</v>
       </c>
       <c r="B72" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8890,7 +8890,7 @@
         <v>135294784</v>
       </c>
       <c r="B73" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9006,7 +9006,7 @@
         <v>135294787</v>
       </c>
       <c r="B74" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9122,7 +9122,7 @@
         <v>135294788</v>
       </c>
       <c r="B75" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9238,7 +9238,7 @@
         <v>135294790</v>
       </c>
       <c r="B76" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9354,7 +9354,7 @@
         <v>135294794</v>
       </c>
       <c r="B77" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9470,7 +9470,7 @@
         <v>135294836</v>
       </c>
       <c r="B78" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9586,7 +9586,7 @@
         <v>135294847</v>
       </c>
       <c r="B79" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9702,7 +9702,7 @@
         <v>135294849</v>
       </c>
       <c r="B80" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9818,7 +9818,7 @@
         <v>135295388</v>
       </c>
       <c r="B81" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9934,7 +9934,7 @@
         <v>135298391</v>
       </c>
       <c r="B82" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10046,7 +10046,7 @@
         <v>135298435</v>
       </c>
       <c r="B83" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10162,7 +10162,7 @@
         <v>135300492</v>
       </c>
       <c r="B84" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10278,7 +10278,7 @@
         <v>135301733</v>
       </c>
       <c r="B85" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10394,7 +10394,7 @@
         <v>135301780</v>
       </c>
       <c r="B86" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10491,7 +10491,7 @@
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Petra Wikström, Pia Edfors</t>
+          <t>Pia Edfors, Petra Wikström</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr">
@@ -10510,7 +10510,7 @@
         <v>135301783</v>
       </c>
       <c r="B87" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10607,7 +10607,7 @@
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Petra Wikström, Pia Edfors</t>
+          <t>Pia Edfors, Petra Wikström</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr">
@@ -10626,7 +10626,7 @@
         <v>135294793</v>
       </c>
       <c r="B88" t="n">
-        <v>80492</v>
+        <v>80530</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10742,7 +10742,7 @@
         <v>135294360</v>
       </c>
       <c r="B89" t="n">
-        <v>57162</v>
+        <v>57167</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10864,7 +10864,7 @@
         <v>135294378</v>
       </c>
       <c r="B90" t="n">
-        <v>57162</v>
+        <v>57167</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10989,7 +10989,7 @@
         <v>135294789</v>
       </c>
       <c r="B91" t="n">
-        <v>57162</v>
+        <v>57167</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11110,7 +11110,7 @@
         <v>135298432</v>
       </c>
       <c r="B92" t="n">
-        <v>57162</v>
+        <v>57167</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11226,7 +11226,7 @@
         <v>135300490</v>
       </c>
       <c r="B93" t="n">
-        <v>57162</v>
+        <v>57167</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11347,7 +11347,7 @@
         <v>135301804</v>
       </c>
       <c r="B94" t="n">
-        <v>57165</v>
+        <v>57170</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11468,7 +11468,7 @@
         <v>135301738</v>
       </c>
       <c r="B95" t="n">
-        <v>58079</v>
+        <v>58084</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11589,7 +11589,7 @@
         <v>135301803</v>
       </c>
       <c r="B96" t="n">
-        <v>8449</v>
+        <v>8450</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11710,7 +11710,7 @@
         <v>135294357</v>
       </c>
       <c r="B97" t="n">
-        <v>98066</v>
+        <v>98110</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11822,7 +11822,7 @@
         <v>135294781</v>
       </c>
       <c r="B98" t="n">
-        <v>98066</v>
+        <v>98110</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11938,7 +11938,7 @@
         <v>135294843</v>
       </c>
       <c r="B99" t="n">
-        <v>98066</v>
+        <v>98110</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -12054,7 +12054,7 @@
         <v>135295389</v>
       </c>
       <c r="B100" t="n">
-        <v>98066</v>
+        <v>98110</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -12175,7 +12175,7 @@
         <v>135300497</v>
       </c>
       <c r="B101" t="n">
-        <v>98066</v>
+        <v>98110</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -12291,7 +12291,7 @@
         <v>135301728</v>
       </c>
       <c r="B102" t="n">
-        <v>98060</v>
+        <v>98104</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12407,7 +12407,7 @@
         <v>135301791</v>
       </c>
       <c r="B103" t="n">
-        <v>98060</v>
+        <v>98104</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12523,7 +12523,7 @@
         <v>135295379</v>
       </c>
       <c r="B104" t="n">
-        <v>79131</v>
+        <v>79169</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12639,7 +12639,7 @@
         <v>135300488</v>
       </c>
       <c r="B105" t="n">
-        <v>79131</v>
+        <v>79169</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12755,7 +12755,7 @@
         <v>135300493</v>
       </c>
       <c r="B106" t="n">
-        <v>79131</v>
+        <v>79169</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12871,7 +12871,7 @@
         <v>135301778</v>
       </c>
       <c r="B107" t="n">
-        <v>79131</v>
+        <v>79169</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12987,7 +12987,7 @@
         <v>135301796</v>
       </c>
       <c r="B108" t="n">
-        <v>79131</v>
+        <v>79169</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -13103,7 +13103,7 @@
         <v>135294355</v>
       </c>
       <c r="B109" t="n">
-        <v>79963</v>
+        <v>80001</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -13215,7 +13215,7 @@
         <v>135294785</v>
       </c>
       <c r="B110" t="n">
-        <v>79963</v>
+        <v>80001</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -13331,7 +13331,7 @@
         <v>135295378</v>
       </c>
       <c r="B111" t="n">
-        <v>79963</v>
+        <v>80001</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13447,7 +13447,7 @@
         <v>135295386</v>
       </c>
       <c r="B112" t="n">
-        <v>79963</v>
+        <v>80001</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13563,7 +13563,7 @@
         <v>135295387</v>
       </c>
       <c r="B113" t="n">
-        <v>79963</v>
+        <v>80001</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13679,7 +13679,7 @@
         <v>135298403</v>
       </c>
       <c r="B114" t="n">
-        <v>79963</v>
+        <v>80001</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13791,7 +13791,7 @@
         <v>135300489</v>
       </c>
       <c r="B115" t="n">
-        <v>79963</v>
+        <v>80001</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13907,7 +13907,7 @@
         <v>135300491</v>
       </c>
       <c r="B116" t="n">
-        <v>79963</v>
+        <v>80001</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -14023,7 +14023,7 @@
         <v>135300574</v>
       </c>
       <c r="B117" t="n">
-        <v>79963</v>
+        <v>80001</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -14139,7 +14139,7 @@
         <v>135300575</v>
       </c>
       <c r="B118" t="n">
-        <v>79963</v>
+        <v>80001</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -14255,7 +14255,7 @@
         <v>135301794</v>
       </c>
       <c r="B119" t="n">
-        <v>79963</v>
+        <v>80001</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -14371,7 +14371,7 @@
         <v>135291042</v>
       </c>
       <c r="B120" t="n">
-        <v>79396</v>
+        <v>79434</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -14483,7 +14483,7 @@
         <v>135294356</v>
       </c>
       <c r="B121" t="n">
-        <v>79396</v>
+        <v>79434</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -14595,7 +14595,7 @@
         <v>135294362</v>
       </c>
       <c r="B122" t="n">
-        <v>79396</v>
+        <v>79434</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14707,7 +14707,7 @@
         <v>135294796</v>
       </c>
       <c r="B123" t="n">
-        <v>79396</v>
+        <v>79434</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14823,7 +14823,7 @@
         <v>135294853</v>
       </c>
       <c r="B124" t="n">
-        <v>79396</v>
+        <v>79434</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14939,7 +14939,7 @@
         <v>135295384</v>
       </c>
       <c r="B125" t="n">
-        <v>79396</v>
+        <v>79434</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -15055,7 +15055,7 @@
         <v>135295385</v>
       </c>
       <c r="B126" t="n">
-        <v>79396</v>
+        <v>79434</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -15172,7 +15172,7 @@
         <v>135301727</v>
       </c>
       <c r="B127" t="n">
-        <v>79396</v>
+        <v>79434</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -15288,7 +15288,7 @@
         <v>135301735</v>
       </c>
       <c r="B128" t="n">
-        <v>79396</v>
+        <v>79434</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -15404,7 +15404,7 @@
         <v>135295442</v>
       </c>
       <c r="B129" t="n">
-        <v>93292</v>
+        <v>93334</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -15524,7 +15524,7 @@
         <v>135301801</v>
       </c>
       <c r="B130" t="n">
-        <v>93292</v>
+        <v>93334</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15636,7 +15636,7 @@
         <v>135300502</v>
       </c>
       <c r="B131" t="n">
-        <v>92220</v>
+        <v>92262</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -16160,7 +16160,7 @@
         <v>135294374</v>
       </c>
       <c r="B136" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -16272,7 +16272,7 @@
         <v>135294800</v>
       </c>
       <c r="B137" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -16388,7 +16388,7 @@
         <v>135294823</v>
       </c>
       <c r="B138" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -16504,7 +16504,7 @@
         <v>135294824</v>
       </c>
       <c r="B139" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -16620,7 +16620,7 @@
         <v>135298439</v>
       </c>
       <c r="B140" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -16736,7 +16736,7 @@
         <v>135298457</v>
       </c>
       <c r="B141" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -16852,7 +16852,7 @@
         <v>135298458</v>
       </c>
       <c r="B142" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -16968,7 +16968,7 @@
         <v>135300504</v>
       </c>
       <c r="B143" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -17084,7 +17084,7 @@
         <v>135300508</v>
       </c>
       <c r="B144" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -17205,7 +17205,7 @@
         <v>135300511</v>
       </c>
       <c r="B145" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -17326,7 +17326,7 @@
         <v>135300526</v>
       </c>
       <c r="B146" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -17442,7 +17442,7 @@
         <v>135300531</v>
       </c>
       <c r="B147" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -17558,7 +17558,7 @@
         <v>135300534</v>
       </c>
       <c r="B148" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -17679,7 +17679,7 @@
         <v>135300537</v>
       </c>
       <c r="B149" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -17795,7 +17795,7 @@
         <v>135300541</v>
       </c>
       <c r="B150" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -17911,7 +17911,7 @@
         <v>135300552</v>
       </c>
       <c r="B151" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -18027,7 +18027,7 @@
         <v>135300555</v>
       </c>
       <c r="B152" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -18143,7 +18143,7 @@
         <v>135300560</v>
       </c>
       <c r="B153" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -18259,7 +18259,7 @@
         <v>135300561</v>
       </c>
       <c r="B154" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -18375,7 +18375,7 @@
         <v>135300562</v>
       </c>
       <c r="B155" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -18496,7 +18496,7 @@
         <v>135300568</v>
       </c>
       <c r="B156" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -18612,7 +18612,7 @@
         <v>135300569</v>
       </c>
       <c r="B157" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -18728,7 +18728,7 @@
         <v>135301768</v>
       </c>
       <c r="B158" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -18844,7 +18844,7 @@
         <v>135294811</v>
       </c>
       <c r="B159" t="n">
-        <v>92245</v>
+        <v>92287</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -18960,7 +18960,7 @@
         <v>135300523</v>
       </c>
       <c r="B160" t="n">
-        <v>79452</v>
+        <v>79490</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -19076,7 +19076,7 @@
         <v>135301784</v>
       </c>
       <c r="B161" t="n">
-        <v>79452</v>
+        <v>79490</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -19174,7 +19174,7 @@
       </c>
       <c r="AX161" t="inlineStr">
         <is>
-          <t>Petra Wikström, Pia Edfors</t>
+          <t>Pia Edfors, Petra Wikström</t>
         </is>
       </c>
       <c r="AY161" t="inlineStr">
@@ -19193,7 +19193,7 @@
         <v>135300510</v>
       </c>
       <c r="B162" t="n">
-        <v>81355</v>
+        <v>81393</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -19411,7 +19411,7 @@
         <v>135298436</v>
       </c>
       <c r="B164" t="n">
-        <v>92153</v>
+        <v>92195</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -19527,7 +19527,7 @@
         <v>135298437</v>
       </c>
       <c r="B165" t="n">
-        <v>92153</v>
+        <v>92195</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -19643,7 +19643,7 @@
         <v>135300514</v>
       </c>
       <c r="B166" t="n">
-        <v>92153</v>
+        <v>92195</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -19759,7 +19759,7 @@
         <v>135300540</v>
       </c>
       <c r="B167" t="n">
-        <v>92153</v>
+        <v>92195</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -19875,7 +19875,7 @@
         <v>135300566</v>
       </c>
       <c r="B168" t="n">
-        <v>92153</v>
+        <v>92195</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -20297,7 +20297,7 @@
         <v>135300513</v>
       </c>
       <c r="B172" t="n">
-        <v>92027</v>
+        <v>92069</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -20413,7 +20413,7 @@
         <v>135300516</v>
       </c>
       <c r="B173" t="n">
-        <v>92027</v>
+        <v>92069</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -20529,7 +20529,7 @@
         <v>135300519</v>
       </c>
       <c r="B174" t="n">
-        <v>92027</v>
+        <v>92069</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -20747,7 +20747,7 @@
         <v>135300542</v>
       </c>
       <c r="B176" t="n">
-        <v>91896</v>
+        <v>91938</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -20863,7 +20863,7 @@
         <v>135294839</v>
       </c>
       <c r="B177" t="n">
-        <v>93271</v>
+        <v>93313</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -20979,7 +20979,7 @@
         <v>135298447</v>
       </c>
       <c r="B178" t="n">
-        <v>93271</v>
+        <v>93313</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -21095,7 +21095,7 @@
         <v>135301769</v>
       </c>
       <c r="B179" t="n">
-        <v>93271</v>
+        <v>93313</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -21318,7 +21318,7 @@
         <v>135300520</v>
       </c>
       <c r="B181" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -21638,7 +21638,7 @@
         <v>135300509</v>
       </c>
       <c r="B184" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -21754,7 +21754,7 @@
         <v>135300525</v>
       </c>
       <c r="B185" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -21870,7 +21870,7 @@
         <v>135300529</v>
       </c>
       <c r="B186" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -22700,7 +22700,7 @@
         <v>135294821</v>
       </c>
       <c r="B194" t="n">
-        <v>79130</v>
+        <v>79168</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -22816,7 +22816,7 @@
         <v>135298443</v>
       </c>
       <c r="B195" t="n">
-        <v>79130</v>
+        <v>79168</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -22932,7 +22932,7 @@
         <v>135300507</v>
       </c>
       <c r="B196" t="n">
-        <v>79130</v>
+        <v>79168</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -23048,7 +23048,7 @@
         <v>135300515</v>
       </c>
       <c r="B197" t="n">
-        <v>79130</v>
+        <v>79168</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -23164,7 +23164,7 @@
         <v>135300521</v>
       </c>
       <c r="B198" t="n">
-        <v>79130</v>
+        <v>79168</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -23280,7 +23280,7 @@
         <v>135301762</v>
       </c>
       <c r="B199" t="n">
-        <v>79130</v>
+        <v>79168</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -23804,7 +23804,7 @@
         <v>135294373</v>
       </c>
       <c r="B204" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -23916,7 +23916,7 @@
         <v>135294375</v>
       </c>
       <c r="B205" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -24028,7 +24028,7 @@
         <v>135294799</v>
       </c>
       <c r="B206" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -24144,7 +24144,7 @@
         <v>135294813</v>
       </c>
       <c r="B207" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -24260,7 +24260,7 @@
         <v>135294820</v>
       </c>
       <c r="B208" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -24376,7 +24376,7 @@
         <v>135294840</v>
       </c>
       <c r="B209" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -24492,7 +24492,7 @@
         <v>135298459</v>
       </c>
       <c r="B210" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -24608,7 +24608,7 @@
         <v>135300498</v>
       </c>
       <c r="B211" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -24724,7 +24724,7 @@
         <v>135300503</v>
       </c>
       <c r="B212" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -24840,7 +24840,7 @@
         <v>135300517</v>
       </c>
       <c r="B213" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -24956,7 +24956,7 @@
         <v>135300530</v>
       </c>
       <c r="B214" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -25072,7 +25072,7 @@
         <v>135300532</v>
       </c>
       <c r="B215" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -25188,7 +25188,7 @@
         <v>135300536</v>
       </c>
       <c r="B216" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -25304,7 +25304,7 @@
         <v>135300547</v>
       </c>
       <c r="B217" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -25420,7 +25420,7 @@
         <v>135300548</v>
       </c>
       <c r="B218" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -25536,7 +25536,7 @@
         <v>135300551</v>
       </c>
       <c r="B219" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -25652,7 +25652,7 @@
         <v>135300565</v>
       </c>
       <c r="B220" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -25768,7 +25768,7 @@
         <v>135301743</v>
       </c>
       <c r="B221" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -25884,7 +25884,7 @@
         <v>135301764</v>
       </c>
       <c r="B222" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -26000,7 +26000,7 @@
         <v>135301774</v>
       </c>
       <c r="B223" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -26116,7 +26116,7 @@
         <v>135301786</v>
       </c>
       <c r="B224" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -26232,7 +26232,7 @@
         <v>135301788</v>
       </c>
       <c r="B225" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -26348,7 +26348,7 @@
         <v>135300544</v>
       </c>
       <c r="B226" t="n">
-        <v>80382</v>
+        <v>80420</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -26464,7 +26464,7 @@
         <v>135300545</v>
       </c>
       <c r="B227" t="n">
-        <v>80382</v>
+        <v>80420</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -26784,7 +26784,7 @@
         <v>135294807</v>
       </c>
       <c r="B230" t="n">
-        <v>80493</v>
+        <v>80531</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -26900,7 +26900,7 @@
         <v>135294815</v>
       </c>
       <c r="B231" t="n">
-        <v>80493</v>
+        <v>80531</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -27016,7 +27016,7 @@
         <v>135301748</v>
       </c>
       <c r="B232" t="n">
-        <v>80493</v>
+        <v>80531</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -27336,7 +27336,7 @@
         <v>135294805</v>
       </c>
       <c r="B235" t="n">
-        <v>80499</v>
+        <v>80537</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -27452,7 +27452,7 @@
         <v>135301749</v>
       </c>
       <c r="B236" t="n">
-        <v>80499</v>
+        <v>80537</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -27568,7 +27568,7 @@
         <v>135301754</v>
       </c>
       <c r="B237" t="n">
-        <v>80499</v>
+        <v>80537</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -27786,7 +27786,7 @@
         <v>135301751</v>
       </c>
       <c r="B239" t="n">
-        <v>80500</v>
+        <v>80538</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -28106,7 +28106,7 @@
         <v>135300527</v>
       </c>
       <c r="B242" t="n">
-        <v>78377</v>
+        <v>78415</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -28222,7 +28222,7 @@
         <v>135294809</v>
       </c>
       <c r="B243" t="n">
-        <v>57972</v>
+        <v>57977</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -28338,7 +28338,7 @@
         <v>135300506</v>
       </c>
       <c r="B244" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -28459,7 +28459,7 @@
         <v>135300543</v>
       </c>
       <c r="B245" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -28687,7 +28687,7 @@
         <v>135294810</v>
       </c>
       <c r="B247" t="n">
-        <v>57162</v>
+        <v>57167</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -28808,7 +28808,7 @@
         <v>135298406</v>
       </c>
       <c r="B248" t="n">
-        <v>57162</v>
+        <v>57167</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -28937,7 +28937,7 @@
         <v>135298438</v>
       </c>
       <c r="B249" t="n">
-        <v>57162</v>
+        <v>57167</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -29053,7 +29053,7 @@
         <v>135298440</v>
       </c>
       <c r="B250" t="n">
-        <v>57162</v>
+        <v>57167</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -29174,7 +29174,7 @@
         <v>135298445</v>
       </c>
       <c r="B251" t="n">
-        <v>57162</v>
+        <v>57167</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -29295,7 +29295,7 @@
         <v>135300553</v>
       </c>
       <c r="B252" t="n">
-        <v>57162</v>
+        <v>57167</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -29416,7 +29416,7 @@
         <v>135300563</v>
       </c>
       <c r="B253" t="n">
-        <v>57162</v>
+        <v>57167</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -29537,7 +29537,7 @@
         <v>135300567</v>
       </c>
       <c r="B254" t="n">
-        <v>57162</v>
+        <v>57167</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -29760,7 +29760,7 @@
         <v>135301755</v>
       </c>
       <c r="B256" t="n">
-        <v>58136</v>
+        <v>58141</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -29876,7 +29876,7 @@
         <v>135294377</v>
       </c>
       <c r="B257" t="n">
-        <v>58079</v>
+        <v>58084</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -29997,7 +29997,7 @@
         <v>135300538</v>
       </c>
       <c r="B258" t="n">
-        <v>58079</v>
+        <v>58084</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -30122,7 +30122,7 @@
         <v>135300501</v>
       </c>
       <c r="B259" t="n">
-        <v>56706</v>
+        <v>56711</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -30238,7 +30238,7 @@
         <v>135301756</v>
       </c>
       <c r="B260" t="n">
-        <v>111153</v>
+        <v>111210</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -30354,7 +30354,7 @@
         <v>135294816</v>
       </c>
       <c r="B261" t="n">
-        <v>106309</v>
+        <v>106364</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -30470,7 +30470,7 @@
         <v>135301744</v>
       </c>
       <c r="B262" t="n">
-        <v>106309</v>
+        <v>106364</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -30586,7 +30586,7 @@
         <v>135294825</v>
       </c>
       <c r="B263" t="n">
-        <v>98066</v>
+        <v>98110</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -30702,7 +30702,7 @@
         <v>135301741</v>
       </c>
       <c r="B264" t="n">
-        <v>98066</v>
+        <v>98110</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -30818,7 +30818,7 @@
         <v>135301757</v>
       </c>
       <c r="B265" t="n">
-        <v>98066</v>
+        <v>98110</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -30934,7 +30934,7 @@
         <v>135301766</v>
       </c>
       <c r="B266" t="n">
-        <v>98066</v>
+        <v>98110</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -31050,7 +31050,7 @@
         <v>135301770</v>
       </c>
       <c r="B267" t="n">
-        <v>98066</v>
+        <v>98110</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -31166,7 +31166,7 @@
         <v>135301790</v>
       </c>
       <c r="B268" t="n">
-        <v>98066</v>
+        <v>98110</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -31282,7 +31282,7 @@
         <v>135298442</v>
       </c>
       <c r="B269" t="n">
-        <v>98060</v>
+        <v>98104</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -31398,7 +31398,7 @@
         <v>135301747</v>
       </c>
       <c r="B270" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -31514,7 +31514,7 @@
         <v>135301759</v>
       </c>
       <c r="B271" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -31630,7 +31630,7 @@
         <v>135295146</v>
       </c>
       <c r="B272" t="n">
-        <v>100806</v>
+        <v>100854</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -31950,7 +31950,7 @@
         <v>135298444</v>
       </c>
       <c r="B275" t="n">
-        <v>79131</v>
+        <v>79169</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -32066,7 +32066,7 @@
         <v>135298446</v>
       </c>
       <c r="B276" t="n">
-        <v>79131</v>
+        <v>79169</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -32182,7 +32182,7 @@
         <v>135300550</v>
       </c>
       <c r="B277" t="n">
-        <v>79131</v>
+        <v>79169</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -32298,7 +32298,7 @@
         <v>135301752</v>
       </c>
       <c r="B278" t="n">
-        <v>80438</v>
+        <v>80476</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -32516,7 +32516,7 @@
         <v>135294801</v>
       </c>
       <c r="B280" t="n">
-        <v>79963</v>
+        <v>80001</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -32632,7 +32632,7 @@
         <v>135294812</v>
       </c>
       <c r="B281" t="n">
-        <v>79963</v>
+        <v>80001</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -32748,7 +32748,7 @@
         <v>135298407</v>
       </c>
       <c r="B282" t="n">
-        <v>79963</v>
+        <v>80001</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -32860,7 +32860,7 @@
         <v>135300524</v>
       </c>
       <c r="B283" t="n">
-        <v>79963</v>
+        <v>80001</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -32976,7 +32976,7 @@
         <v>135300528</v>
       </c>
       <c r="B284" t="n">
-        <v>79963</v>
+        <v>80001</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -33092,7 +33092,7 @@
         <v>135300533</v>
       </c>
       <c r="B285" t="n">
-        <v>79963</v>
+        <v>80001</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -33208,7 +33208,7 @@
         <v>135300539</v>
       </c>
       <c r="B286" t="n">
-        <v>79963</v>
+        <v>80001</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -33324,7 +33324,7 @@
         <v>135300546</v>
       </c>
       <c r="B287" t="n">
-        <v>79963</v>
+        <v>80001</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -33440,7 +33440,7 @@
         <v>135300549</v>
       </c>
       <c r="B288" t="n">
-        <v>79963</v>
+        <v>80001</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -33556,7 +33556,7 @@
         <v>135300554</v>
       </c>
       <c r="B289" t="n">
-        <v>79963</v>
+        <v>80001</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -33672,7 +33672,7 @@
         <v>135300557</v>
       </c>
       <c r="B290" t="n">
-        <v>79963</v>
+        <v>80001</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -33788,7 +33788,7 @@
         <v>135300564</v>
       </c>
       <c r="B291" t="n">
-        <v>79963</v>
+        <v>80001</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -33904,7 +33904,7 @@
         <v>135301787</v>
       </c>
       <c r="B292" t="n">
-        <v>79963</v>
+        <v>80001</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -34020,7 +34020,7 @@
         <v>135294376</v>
       </c>
       <c r="B293" t="n">
-        <v>79396</v>
+        <v>79434</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -34132,7 +34132,7 @@
         <v>135294835</v>
       </c>
       <c r="B294" t="n">
-        <v>79396</v>
+        <v>79434</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -34248,7 +34248,7 @@
         <v>135300505</v>
       </c>
       <c r="B295" t="n">
-        <v>79396</v>
+        <v>79434</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -34369,7 +34369,7 @@
         <v>135301765</v>
       </c>
       <c r="B296" t="n">
-        <v>79396</v>
+        <v>79434</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -34485,7 +34485,7 @@
         <v>135301773</v>
       </c>
       <c r="B297" t="n">
-        <v>79396</v>
+        <v>79434</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>

--- a/artfynd/Gålggåmisvárre artfynd.xlsx
+++ b/artfynd/Gålggåmisvárre artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135294829</v>
       </c>
       <c r="B2" t="n">
-        <v>93307</v>
+        <v>93334</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>135301776</v>
       </c>
       <c r="B3" t="n">
-        <v>93313</v>
+        <v>93340</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>135294818</v>
       </c>
       <c r="B4" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1041,7 +1041,7 @@
         <v>135294827</v>
       </c>
       <c r="B5" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1157,7 +1157,7 @@
         <v>135294830</v>
       </c>
       <c r="B6" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1273,7 +1273,7 @@
         <v>135294834</v>
       </c>
       <c r="B7" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1509,7 +1509,7 @@
         <v>135294841</v>
       </c>
       <c r="B9" t="n">
-        <v>98110</v>
+        <v>98137</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1625,7 +1625,7 @@
         <v>135294826</v>
       </c>
       <c r="B10" t="n">
-        <v>80001</v>
+        <v>80028</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         <v>135294833</v>
       </c>
       <c r="B11" t="n">
-        <v>80001</v>
+        <v>80028</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1857,7 +1857,7 @@
         <v>135294828</v>
       </c>
       <c r="B12" t="n">
-        <v>79434</v>
+        <v>79461</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1973,7 +1973,7 @@
         <v>135294831</v>
       </c>
       <c r="B13" t="n">
-        <v>79434</v>
+        <v>79461</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2191,7 +2191,7 @@
         <v>135295377</v>
       </c>
       <c r="B15" t="n">
-        <v>92262</v>
+        <v>92289</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2311,7 +2311,7 @@
         <v>135294352</v>
       </c>
       <c r="B16" t="n">
-        <v>92411</v>
+        <v>92438</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2553,7 +2553,7 @@
         <v>135294350</v>
       </c>
       <c r="B18" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2703,7 +2703,7 @@
         <v>135294354</v>
       </c>
       <c r="B19" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2815,7 +2815,7 @@
         <v>135294364</v>
       </c>
       <c r="B20" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2927,7 +2927,7 @@
         <v>135294783</v>
       </c>
       <c r="B21" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3043,7 +3043,7 @@
         <v>135294791</v>
       </c>
       <c r="B22" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3159,7 +3159,7 @@
         <v>135294837</v>
       </c>
       <c r="B23" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3275,7 +3275,7 @@
         <v>135294850</v>
       </c>
       <c r="B24" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3391,7 +3391,7 @@
         <v>135294854</v>
       </c>
       <c r="B25" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3507,7 +3507,7 @@
         <v>135295381</v>
       </c>
       <c r="B26" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3623,7 +3623,7 @@
         <v>135295383</v>
       </c>
       <c r="B27" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3739,7 +3739,7 @@
         <v>135298434</v>
       </c>
       <c r="B28" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3855,7 +3855,7 @@
         <v>135300485</v>
       </c>
       <c r="B29" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3971,7 +3971,7 @@
         <v>135300494</v>
       </c>
       <c r="B30" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4087,7 +4087,7 @@
         <v>135300500</v>
       </c>
       <c r="B31" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4203,7 +4203,7 @@
         <v>135300572</v>
       </c>
       <c r="B32" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4324,7 +4324,7 @@
         <v>135301725</v>
       </c>
       <c r="B33" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4440,7 +4440,7 @@
         <v>135301737</v>
       </c>
       <c r="B34" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4556,7 +4556,7 @@
         <v>135301777</v>
       </c>
       <c r="B35" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4672,7 +4672,7 @@
         <v>135301793</v>
       </c>
       <c r="B36" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4788,7 +4788,7 @@
         <v>135294795</v>
       </c>
       <c r="B37" t="n">
-        <v>79490</v>
+        <v>79517</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4904,7 +4904,7 @@
         <v>135301800</v>
       </c>
       <c r="B38" t="n">
-        <v>81393</v>
+        <v>81420</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5122,7 +5122,7 @@
         <v>135294361</v>
       </c>
       <c r="B40" t="n">
-        <v>92195</v>
+        <v>92222</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5254,7 +5254,7 @@
         <v>135295390</v>
       </c>
       <c r="B41" t="n">
-        <v>92195</v>
+        <v>92222</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5370,7 +5370,7 @@
         <v>135298393</v>
       </c>
       <c r="B42" t="n">
-        <v>92195</v>
+        <v>92222</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5482,7 +5482,7 @@
         <v>135298394</v>
       </c>
       <c r="B43" t="n">
-        <v>92195</v>
+        <v>92222</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5594,7 +5594,7 @@
         <v>135298401</v>
       </c>
       <c r="B44" t="n">
-        <v>92195</v>
+        <v>92222</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5706,7 +5706,7 @@
         <v>135300576</v>
       </c>
       <c r="B45" t="n">
-        <v>92195</v>
+        <v>92222</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6026,7 +6026,7 @@
         <v>135294851</v>
       </c>
       <c r="B48" t="n">
-        <v>91039</v>
+        <v>91066</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6244,7 +6244,7 @@
         <v>135294365</v>
       </c>
       <c r="B50" t="n">
-        <v>92069</v>
+        <v>92096</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6356,7 +6356,7 @@
         <v>135300496</v>
       </c>
       <c r="B51" t="n">
-        <v>92069</v>
+        <v>92096</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6472,7 +6472,7 @@
         <v>135301730</v>
       </c>
       <c r="B52" t="n">
-        <v>92069</v>
+        <v>92096</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6588,7 +6588,7 @@
         <v>135294359</v>
       </c>
       <c r="B53" t="n">
-        <v>91938</v>
+        <v>91965</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6700,7 +6700,7 @@
         <v>135294363</v>
       </c>
       <c r="B54" t="n">
-        <v>93313</v>
+        <v>93340</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6812,7 +6812,7 @@
         <v>135294852</v>
       </c>
       <c r="B55" t="n">
-        <v>93313</v>
+        <v>93340</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6928,7 +6928,7 @@
         <v>135301781</v>
       </c>
       <c r="B56" t="n">
-        <v>93313</v>
+        <v>93340</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7151,7 +7151,7 @@
         <v>135301740</v>
       </c>
       <c r="B58" t="n">
-        <v>93317</v>
+        <v>93344</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7267,7 +7267,7 @@
         <v>135294351</v>
       </c>
       <c r="B59" t="n">
-        <v>91979</v>
+        <v>92006</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7414,7 +7414,7 @@
         <v>135300495</v>
       </c>
       <c r="B60" t="n">
-        <v>91979</v>
+        <v>92006</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7530,7 +7530,7 @@
         <v>135301732</v>
       </c>
       <c r="B61" t="n">
-        <v>91979</v>
+        <v>92006</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7646,7 +7646,7 @@
         <v>135301797</v>
       </c>
       <c r="B62" t="n">
-        <v>91979</v>
+        <v>92006</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7762,7 +7762,7 @@
         <v>135294358</v>
       </c>
       <c r="B63" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7874,7 +7874,7 @@
         <v>135294797</v>
       </c>
       <c r="B64" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7990,7 +7990,7 @@
         <v>135298397</v>
       </c>
       <c r="B65" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8102,7 +8102,7 @@
         <v>135298398</v>
       </c>
       <c r="B66" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8222,7 +8222,7 @@
         <v>135298433</v>
       </c>
       <c r="B67" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8338,7 +8338,7 @@
         <v>135300487</v>
       </c>
       <c r="B68" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8556,7 +8556,7 @@
         <v>135295380</v>
       </c>
       <c r="B70" t="n">
-        <v>79168</v>
+        <v>79195</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8774,7 +8774,7 @@
         <v>135294782</v>
       </c>
       <c r="B72" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8890,7 +8890,7 @@
         <v>135294784</v>
       </c>
       <c r="B73" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9006,7 +9006,7 @@
         <v>135294787</v>
       </c>
       <c r="B74" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9122,7 +9122,7 @@
         <v>135294788</v>
       </c>
       <c r="B75" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9238,7 +9238,7 @@
         <v>135294790</v>
       </c>
       <c r="B76" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9354,7 +9354,7 @@
         <v>135294794</v>
       </c>
       <c r="B77" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9470,7 +9470,7 @@
         <v>135294836</v>
       </c>
       <c r="B78" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9586,7 +9586,7 @@
         <v>135294847</v>
       </c>
       <c r="B79" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9702,7 +9702,7 @@
         <v>135294849</v>
       </c>
       <c r="B80" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9818,7 +9818,7 @@
         <v>135295388</v>
       </c>
       <c r="B81" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9934,7 +9934,7 @@
         <v>135298391</v>
       </c>
       <c r="B82" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10046,7 +10046,7 @@
         <v>135298435</v>
       </c>
       <c r="B83" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10162,7 +10162,7 @@
         <v>135300492</v>
       </c>
       <c r="B84" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10278,7 +10278,7 @@
         <v>135301733</v>
       </c>
       <c r="B85" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10394,7 +10394,7 @@
         <v>135301780</v>
       </c>
       <c r="B86" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10510,7 +10510,7 @@
         <v>135301783</v>
       </c>
       <c r="B87" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10626,7 +10626,7 @@
         <v>135294793</v>
       </c>
       <c r="B88" t="n">
-        <v>80530</v>
+        <v>80557</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -11710,7 +11710,7 @@
         <v>135294357</v>
       </c>
       <c r="B97" t="n">
-        <v>98110</v>
+        <v>98137</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11822,7 +11822,7 @@
         <v>135294781</v>
       </c>
       <c r="B98" t="n">
-        <v>98110</v>
+        <v>98137</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11938,7 +11938,7 @@
         <v>135294843</v>
       </c>
       <c r="B99" t="n">
-        <v>98110</v>
+        <v>98137</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -12054,7 +12054,7 @@
         <v>135295389</v>
       </c>
       <c r="B100" t="n">
-        <v>98110</v>
+        <v>98137</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -12175,7 +12175,7 @@
         <v>135300497</v>
       </c>
       <c r="B101" t="n">
-        <v>98110</v>
+        <v>98137</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -12291,7 +12291,7 @@
         <v>135301728</v>
       </c>
       <c r="B102" t="n">
-        <v>98104</v>
+        <v>98131</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12407,7 +12407,7 @@
         <v>135301791</v>
       </c>
       <c r="B103" t="n">
-        <v>98104</v>
+        <v>98131</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12523,7 +12523,7 @@
         <v>135295379</v>
       </c>
       <c r="B104" t="n">
-        <v>79169</v>
+        <v>79196</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12639,7 +12639,7 @@
         <v>135300488</v>
       </c>
       <c r="B105" t="n">
-        <v>79169</v>
+        <v>79196</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12755,7 +12755,7 @@
         <v>135300493</v>
       </c>
       <c r="B106" t="n">
-        <v>79169</v>
+        <v>79196</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12871,7 +12871,7 @@
         <v>135301778</v>
       </c>
       <c r="B107" t="n">
-        <v>79169</v>
+        <v>79196</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12987,7 +12987,7 @@
         <v>135301796</v>
       </c>
       <c r="B108" t="n">
-        <v>79169</v>
+        <v>79196</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -13103,7 +13103,7 @@
         <v>135294355</v>
       </c>
       <c r="B109" t="n">
-        <v>80001</v>
+        <v>80028</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -13215,7 +13215,7 @@
         <v>135294785</v>
       </c>
       <c r="B110" t="n">
-        <v>80001</v>
+        <v>80028</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -13331,7 +13331,7 @@
         <v>135295378</v>
       </c>
       <c r="B111" t="n">
-        <v>80001</v>
+        <v>80028</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13447,7 +13447,7 @@
         <v>135295386</v>
       </c>
       <c r="B112" t="n">
-        <v>80001</v>
+        <v>80028</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13563,7 +13563,7 @@
         <v>135295387</v>
       </c>
       <c r="B113" t="n">
-        <v>80001</v>
+        <v>80028</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13679,7 +13679,7 @@
         <v>135298403</v>
       </c>
       <c r="B114" t="n">
-        <v>80001</v>
+        <v>80028</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13791,7 +13791,7 @@
         <v>135300489</v>
       </c>
       <c r="B115" t="n">
-        <v>80001</v>
+        <v>80028</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13907,7 +13907,7 @@
         <v>135300491</v>
       </c>
       <c r="B116" t="n">
-        <v>80001</v>
+        <v>80028</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -14023,7 +14023,7 @@
         <v>135300574</v>
       </c>
       <c r="B117" t="n">
-        <v>80001</v>
+        <v>80028</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -14139,7 +14139,7 @@
         <v>135300575</v>
       </c>
       <c r="B118" t="n">
-        <v>80001</v>
+        <v>80028</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -14255,7 +14255,7 @@
         <v>135301794</v>
       </c>
       <c r="B119" t="n">
-        <v>80001</v>
+        <v>80028</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -14371,7 +14371,7 @@
         <v>135291042</v>
       </c>
       <c r="B120" t="n">
-        <v>79434</v>
+        <v>79461</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -14483,7 +14483,7 @@
         <v>135294356</v>
       </c>
       <c r="B121" t="n">
-        <v>79434</v>
+        <v>79461</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -14595,7 +14595,7 @@
         <v>135294362</v>
       </c>
       <c r="B122" t="n">
-        <v>79434</v>
+        <v>79461</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14707,7 +14707,7 @@
         <v>135294796</v>
       </c>
       <c r="B123" t="n">
-        <v>79434</v>
+        <v>79461</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14823,7 +14823,7 @@
         <v>135294853</v>
       </c>
       <c r="B124" t="n">
-        <v>79434</v>
+        <v>79461</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14939,7 +14939,7 @@
         <v>135295384</v>
       </c>
       <c r="B125" t="n">
-        <v>79434</v>
+        <v>79461</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -15055,7 +15055,7 @@
         <v>135295385</v>
       </c>
       <c r="B126" t="n">
-        <v>79434</v>
+        <v>79461</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -15172,7 +15172,7 @@
         <v>135301727</v>
       </c>
       <c r="B127" t="n">
-        <v>79434</v>
+        <v>79461</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -15288,7 +15288,7 @@
         <v>135301735</v>
       </c>
       <c r="B128" t="n">
-        <v>79434</v>
+        <v>79461</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -15404,7 +15404,7 @@
         <v>135295442</v>
       </c>
       <c r="B129" t="n">
-        <v>93334</v>
+        <v>93361</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -15524,7 +15524,7 @@
         <v>135301801</v>
       </c>
       <c r="B130" t="n">
-        <v>93334</v>
+        <v>93361</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15636,7 +15636,7 @@
         <v>135300502</v>
       </c>
       <c r="B131" t="n">
-        <v>92262</v>
+        <v>92289</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -16160,7 +16160,7 @@
         <v>135294374</v>
       </c>
       <c r="B136" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -16272,7 +16272,7 @@
         <v>135294800</v>
       </c>
       <c r="B137" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -16388,7 +16388,7 @@
         <v>135294823</v>
       </c>
       <c r="B138" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -16504,7 +16504,7 @@
         <v>135294824</v>
       </c>
       <c r="B139" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -16620,7 +16620,7 @@
         <v>135298439</v>
       </c>
       <c r="B140" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -16736,7 +16736,7 @@
         <v>135298457</v>
       </c>
       <c r="B141" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -16852,7 +16852,7 @@
         <v>135298458</v>
       </c>
       <c r="B142" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -16968,7 +16968,7 @@
         <v>135300504</v>
       </c>
       <c r="B143" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -17084,7 +17084,7 @@
         <v>135300508</v>
       </c>
       <c r="B144" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -17205,7 +17205,7 @@
         <v>135300511</v>
       </c>
       <c r="B145" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -17326,7 +17326,7 @@
         <v>135300526</v>
       </c>
       <c r="B146" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -17442,7 +17442,7 @@
         <v>135300531</v>
       </c>
       <c r="B147" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -17558,7 +17558,7 @@
         <v>135300534</v>
       </c>
       <c r="B148" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -17679,7 +17679,7 @@
         <v>135300537</v>
       </c>
       <c r="B149" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -17795,7 +17795,7 @@
         <v>135300541</v>
       </c>
       <c r="B150" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -17911,7 +17911,7 @@
         <v>135300552</v>
       </c>
       <c r="B151" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -18027,7 +18027,7 @@
         <v>135300555</v>
       </c>
       <c r="B152" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -18143,7 +18143,7 @@
         <v>135300560</v>
       </c>
       <c r="B153" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -18259,7 +18259,7 @@
         <v>135300561</v>
       </c>
       <c r="B154" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -18375,7 +18375,7 @@
         <v>135300562</v>
       </c>
       <c r="B155" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -18496,7 +18496,7 @@
         <v>135300568</v>
       </c>
       <c r="B156" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -18612,7 +18612,7 @@
         <v>135300569</v>
       </c>
       <c r="B157" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -18728,7 +18728,7 @@
         <v>135301768</v>
       </c>
       <c r="B158" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -18844,7 +18844,7 @@
         <v>135294811</v>
       </c>
       <c r="B159" t="n">
-        <v>92287</v>
+        <v>92314</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -18960,7 +18960,7 @@
         <v>135300523</v>
       </c>
       <c r="B160" t="n">
-        <v>79490</v>
+        <v>79517</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -19076,7 +19076,7 @@
         <v>135301784</v>
       </c>
       <c r="B161" t="n">
-        <v>79490</v>
+        <v>79517</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -19193,7 +19193,7 @@
         <v>135300510</v>
       </c>
       <c r="B162" t="n">
-        <v>81393</v>
+        <v>81420</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -19411,7 +19411,7 @@
         <v>135298436</v>
       </c>
       <c r="B164" t="n">
-        <v>92195</v>
+        <v>92222</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -19527,7 +19527,7 @@
         <v>135298437</v>
       </c>
       <c r="B165" t="n">
-        <v>92195</v>
+        <v>92222</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -19643,7 +19643,7 @@
         <v>135300514</v>
       </c>
       <c r="B166" t="n">
-        <v>92195</v>
+        <v>92222</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -19759,7 +19759,7 @@
         <v>135300540</v>
       </c>
       <c r="B167" t="n">
-        <v>92195</v>
+        <v>92222</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -19875,7 +19875,7 @@
         <v>135300566</v>
       </c>
       <c r="B168" t="n">
-        <v>92195</v>
+        <v>92222</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -20297,7 +20297,7 @@
         <v>135300513</v>
       </c>
       <c r="B172" t="n">
-        <v>92069</v>
+        <v>92096</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -20413,7 +20413,7 @@
         <v>135300516</v>
       </c>
       <c r="B173" t="n">
-        <v>92069</v>
+        <v>92096</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -20529,7 +20529,7 @@
         <v>135300519</v>
       </c>
       <c r="B174" t="n">
-        <v>92069</v>
+        <v>92096</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -20747,7 +20747,7 @@
         <v>135300542</v>
       </c>
       <c r="B176" t="n">
-        <v>91938</v>
+        <v>91965</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -20863,7 +20863,7 @@
         <v>135294839</v>
       </c>
       <c r="B177" t="n">
-        <v>93313</v>
+        <v>93340</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -20979,7 +20979,7 @@
         <v>135298447</v>
       </c>
       <c r="B178" t="n">
-        <v>93313</v>
+        <v>93340</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -21095,7 +21095,7 @@
         <v>135301769</v>
       </c>
       <c r="B179" t="n">
-        <v>93313</v>
+        <v>93340</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -21318,7 +21318,7 @@
         <v>135300520</v>
       </c>
       <c r="B181" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -21638,7 +21638,7 @@
         <v>135300509</v>
       </c>
       <c r="B184" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -21754,7 +21754,7 @@
         <v>135300525</v>
       </c>
       <c r="B185" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -21870,7 +21870,7 @@
         <v>135300529</v>
       </c>
       <c r="B186" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -22700,7 +22700,7 @@
         <v>135294821</v>
       </c>
       <c r="B194" t="n">
-        <v>79168</v>
+        <v>79195</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -22816,7 +22816,7 @@
         <v>135298443</v>
       </c>
       <c r="B195" t="n">
-        <v>79168</v>
+        <v>79195</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -22932,7 +22932,7 @@
         <v>135300507</v>
       </c>
       <c r="B196" t="n">
-        <v>79168</v>
+        <v>79195</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -23048,7 +23048,7 @@
         <v>135300515</v>
       </c>
       <c r="B197" t="n">
-        <v>79168</v>
+        <v>79195</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -23164,7 +23164,7 @@
         <v>135300521</v>
       </c>
       <c r="B198" t="n">
-        <v>79168</v>
+        <v>79195</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -23280,7 +23280,7 @@
         <v>135301762</v>
       </c>
       <c r="B199" t="n">
-        <v>79168</v>
+        <v>79195</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -23804,7 +23804,7 @@
         <v>135294373</v>
       </c>
       <c r="B204" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -23916,7 +23916,7 @@
         <v>135294375</v>
       </c>
       <c r="B205" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -24028,7 +24028,7 @@
         <v>135294799</v>
       </c>
       <c r="B206" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -24144,7 +24144,7 @@
         <v>135294813</v>
       </c>
       <c r="B207" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -24260,7 +24260,7 @@
         <v>135294820</v>
       </c>
       <c r="B208" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -24376,7 +24376,7 @@
         <v>135294840</v>
       </c>
       <c r="B209" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -24492,7 +24492,7 @@
         <v>135298459</v>
       </c>
       <c r="B210" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -24608,7 +24608,7 @@
         <v>135300498</v>
       </c>
       <c r="B211" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -24724,7 +24724,7 @@
         <v>135300503</v>
       </c>
       <c r="B212" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -24840,7 +24840,7 @@
         <v>135300517</v>
       </c>
       <c r="B213" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -24956,7 +24956,7 @@
         <v>135300530</v>
       </c>
       <c r="B214" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -25072,7 +25072,7 @@
         <v>135300532</v>
       </c>
       <c r="B215" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -25188,7 +25188,7 @@
         <v>135300536</v>
       </c>
       <c r="B216" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -25304,7 +25304,7 @@
         <v>135300547</v>
       </c>
       <c r="B217" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -25420,7 +25420,7 @@
         <v>135300548</v>
       </c>
       <c r="B218" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -25536,7 +25536,7 @@
         <v>135300551</v>
       </c>
       <c r="B219" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -25652,7 +25652,7 @@
         <v>135300565</v>
       </c>
       <c r="B220" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -25768,7 +25768,7 @@
         <v>135301743</v>
       </c>
       <c r="B221" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -25884,7 +25884,7 @@
         <v>135301764</v>
       </c>
       <c r="B222" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -26000,7 +26000,7 @@
         <v>135301774</v>
       </c>
       <c r="B223" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -26116,7 +26116,7 @@
         <v>135301786</v>
       </c>
       <c r="B224" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -26232,7 +26232,7 @@
         <v>135301788</v>
       </c>
       <c r="B225" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -26348,7 +26348,7 @@
         <v>135300544</v>
       </c>
       <c r="B226" t="n">
-        <v>80420</v>
+        <v>80447</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -26464,7 +26464,7 @@
         <v>135300545</v>
       </c>
       <c r="B227" t="n">
-        <v>80420</v>
+        <v>80447</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -26784,7 +26784,7 @@
         <v>135294807</v>
       </c>
       <c r="B230" t="n">
-        <v>80531</v>
+        <v>80558</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -26900,7 +26900,7 @@
         <v>135294815</v>
       </c>
       <c r="B231" t="n">
-        <v>80531</v>
+        <v>80558</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -27016,7 +27016,7 @@
         <v>135301748</v>
       </c>
       <c r="B232" t="n">
-        <v>80531</v>
+        <v>80558</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -27336,7 +27336,7 @@
         <v>135294805</v>
       </c>
       <c r="B235" t="n">
-        <v>80537</v>
+        <v>80564</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -27452,7 +27452,7 @@
         <v>135301749</v>
       </c>
       <c r="B236" t="n">
-        <v>80537</v>
+        <v>80564</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -27568,7 +27568,7 @@
         <v>135301754</v>
       </c>
       <c r="B237" t="n">
-        <v>80537</v>
+        <v>80564</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -27786,7 +27786,7 @@
         <v>135301751</v>
       </c>
       <c r="B239" t="n">
-        <v>80538</v>
+        <v>80565</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -28106,7 +28106,7 @@
         <v>135300527</v>
       </c>
       <c r="B242" t="n">
-        <v>78415</v>
+        <v>78442</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -30238,7 +30238,7 @@
         <v>135301756</v>
       </c>
       <c r="B260" t="n">
-        <v>111210</v>
+        <v>111237</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -30354,7 +30354,7 @@
         <v>135294816</v>
       </c>
       <c r="B261" t="n">
-        <v>106364</v>
+        <v>106391</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -30470,7 +30470,7 @@
         <v>135301744</v>
       </c>
       <c r="B262" t="n">
-        <v>106364</v>
+        <v>106391</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -30586,7 +30586,7 @@
         <v>135294825</v>
       </c>
       <c r="B263" t="n">
-        <v>98110</v>
+        <v>98137</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -30702,7 +30702,7 @@
         <v>135301741</v>
       </c>
       <c r="B264" t="n">
-        <v>98110</v>
+        <v>98137</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -30818,7 +30818,7 @@
         <v>135301757</v>
       </c>
       <c r="B265" t="n">
-        <v>98110</v>
+        <v>98137</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -30934,7 +30934,7 @@
         <v>135301766</v>
       </c>
       <c r="B266" t="n">
-        <v>98110</v>
+        <v>98137</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -31050,7 +31050,7 @@
         <v>135301770</v>
       </c>
       <c r="B267" t="n">
-        <v>98110</v>
+        <v>98137</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -31166,7 +31166,7 @@
         <v>135301790</v>
       </c>
       <c r="B268" t="n">
-        <v>98110</v>
+        <v>98137</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -31282,7 +31282,7 @@
         <v>135298442</v>
       </c>
       <c r="B269" t="n">
-        <v>98104</v>
+        <v>98131</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -31398,7 +31398,7 @@
         <v>135301747</v>
       </c>
       <c r="B270" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -31514,7 +31514,7 @@
         <v>135301759</v>
       </c>
       <c r="B271" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -31630,7 +31630,7 @@
         <v>135295146</v>
       </c>
       <c r="B272" t="n">
-        <v>100854</v>
+        <v>100881</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -31950,7 +31950,7 @@
         <v>135298444</v>
       </c>
       <c r="B275" t="n">
-        <v>79169</v>
+        <v>79196</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -32066,7 +32066,7 @@
         <v>135298446</v>
       </c>
       <c r="B276" t="n">
-        <v>79169</v>
+        <v>79196</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -32182,7 +32182,7 @@
         <v>135300550</v>
       </c>
       <c r="B277" t="n">
-        <v>79169</v>
+        <v>79196</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -32298,7 +32298,7 @@
         <v>135301752</v>
       </c>
       <c r="B278" t="n">
-        <v>80476</v>
+        <v>80503</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -32516,7 +32516,7 @@
         <v>135294801</v>
       </c>
       <c r="B280" t="n">
-        <v>80001</v>
+        <v>80028</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -32632,7 +32632,7 @@
         <v>135294812</v>
       </c>
       <c r="B281" t="n">
-        <v>80001</v>
+        <v>80028</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -32748,7 +32748,7 @@
         <v>135298407</v>
       </c>
       <c r="B282" t="n">
-        <v>80001</v>
+        <v>80028</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -32860,7 +32860,7 @@
         <v>135300524</v>
       </c>
       <c r="B283" t="n">
-        <v>80001</v>
+        <v>80028</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -32976,7 +32976,7 @@
         <v>135300528</v>
       </c>
       <c r="B284" t="n">
-        <v>80001</v>
+        <v>80028</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -33092,7 +33092,7 @@
         <v>135300533</v>
       </c>
       <c r="B285" t="n">
-        <v>80001</v>
+        <v>80028</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -33208,7 +33208,7 @@
         <v>135300539</v>
       </c>
       <c r="B286" t="n">
-        <v>80001</v>
+        <v>80028</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -33324,7 +33324,7 @@
         <v>135300546</v>
       </c>
       <c r="B287" t="n">
-        <v>80001</v>
+        <v>80028</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -33440,7 +33440,7 @@
         <v>135300549</v>
       </c>
       <c r="B288" t="n">
-        <v>80001</v>
+        <v>80028</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -33556,7 +33556,7 @@
         <v>135300554</v>
       </c>
       <c r="B289" t="n">
-        <v>80001</v>
+        <v>80028</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -33672,7 +33672,7 @@
         <v>135300557</v>
       </c>
       <c r="B290" t="n">
-        <v>80001</v>
+        <v>80028</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -33788,7 +33788,7 @@
         <v>135300564</v>
       </c>
       <c r="B291" t="n">
-        <v>80001</v>
+        <v>80028</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -33904,7 +33904,7 @@
         <v>135301787</v>
       </c>
       <c r="B292" t="n">
-        <v>80001</v>
+        <v>80028</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -34020,7 +34020,7 @@
         <v>135294376</v>
       </c>
       <c r="B293" t="n">
-        <v>79434</v>
+        <v>79461</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -34132,7 +34132,7 @@
         <v>135294835</v>
       </c>
       <c r="B294" t="n">
-        <v>79434</v>
+        <v>79461</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -34248,7 +34248,7 @@
         <v>135300505</v>
       </c>
       <c r="B295" t="n">
-        <v>79434</v>
+        <v>79461</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -34369,7 +34369,7 @@
         <v>135301765</v>
       </c>
       <c r="B296" t="n">
-        <v>79434</v>
+        <v>79461</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -34485,7 +34485,7 @@
         <v>135301773</v>
       </c>
       <c r="B297" t="n">
-        <v>79434</v>
+        <v>79461</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>

--- a/artfynd/Gålggåmisvárre artfynd.xlsx
+++ b/artfynd/Gålggåmisvárre artfynd.xlsx
@@ -2292,7 +2292,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn, Ann Normark, Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn, Cecilia Goldkuhl, Ann Normark</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
@@ -3604,7 +3604,7 @@
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn, Ann Normark, Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn, Cecilia Goldkuhl, Ann Normark</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
@@ -3720,7 +3720,7 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn, Ann Normark, Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn, Cecilia Goldkuhl, Ann Normark</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
@@ -5351,7 +5351,7 @@
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn, Ann Normark, Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn, Cecilia Goldkuhl, Ann Normark</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr">
@@ -8653,7 +8653,7 @@
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn, Ann Normark, Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn, Cecilia Goldkuhl, Ann Normark</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr">
@@ -9915,7 +9915,7 @@
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn, Ann Normark, Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn, Cecilia Goldkuhl, Ann Normark</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr">
@@ -12156,7 +12156,7 @@
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn, Ann Normark, Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn, Cecilia Goldkuhl, Ann Normark</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr">
@@ -12620,7 +12620,7 @@
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn, Ann Normark, Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn, Cecilia Goldkuhl, Ann Normark</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr">
@@ -13428,7 +13428,7 @@
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn, Ann Normark, Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn, Cecilia Goldkuhl, Ann Normark</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr">
@@ -13544,7 +13544,7 @@
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn, Ann Normark, Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn, Cecilia Goldkuhl, Ann Normark</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr">
@@ -13660,7 +13660,7 @@
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn, Ann Normark, Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn, Cecilia Goldkuhl, Ann Normark</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr">
@@ -15036,7 +15036,7 @@
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn, Ann Normark, Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn, Cecilia Goldkuhl, Ann Normark</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr">
@@ -15153,7 +15153,7 @@
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn, Ann Normark, Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn, Cecilia Goldkuhl, Ann Normark</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr">

--- a/artfynd/Gålggåmisvárre artfynd.xlsx
+++ b/artfynd/Gålggåmisvárre artfynd.xlsx
@@ -2292,7 +2292,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn, Cecilia Goldkuhl, Ann Normark</t>
+          <t>Linda-Marie Grahn, Ann Normark, Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
@@ -3604,7 +3604,7 @@
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn, Cecilia Goldkuhl, Ann Normark</t>
+          <t>Linda-Marie Grahn, Ann Normark, Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
@@ -3720,7 +3720,7 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn, Cecilia Goldkuhl, Ann Normark</t>
+          <t>Linda-Marie Grahn, Ann Normark, Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
@@ -5351,7 +5351,7 @@
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn, Cecilia Goldkuhl, Ann Normark</t>
+          <t>Linda-Marie Grahn, Ann Normark, Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr">
@@ -8653,7 +8653,7 @@
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn, Cecilia Goldkuhl, Ann Normark</t>
+          <t>Linda-Marie Grahn, Ann Normark, Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr">
@@ -9915,7 +9915,7 @@
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn, Cecilia Goldkuhl, Ann Normark</t>
+          <t>Linda-Marie Grahn, Ann Normark, Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr">
@@ -12156,7 +12156,7 @@
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn, Cecilia Goldkuhl, Ann Normark</t>
+          <t>Linda-Marie Grahn, Ann Normark, Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr">
@@ -12620,7 +12620,7 @@
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn, Cecilia Goldkuhl, Ann Normark</t>
+          <t>Linda-Marie Grahn, Ann Normark, Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr">
@@ -13428,7 +13428,7 @@
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn, Cecilia Goldkuhl, Ann Normark</t>
+          <t>Linda-Marie Grahn, Ann Normark, Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr">
@@ -13544,7 +13544,7 @@
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn, Cecilia Goldkuhl, Ann Normark</t>
+          <t>Linda-Marie Grahn, Ann Normark, Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr">
@@ -13660,7 +13660,7 @@
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn, Cecilia Goldkuhl, Ann Normark</t>
+          <t>Linda-Marie Grahn, Ann Normark, Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr">
@@ -15036,7 +15036,7 @@
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn, Cecilia Goldkuhl, Ann Normark</t>
+          <t>Linda-Marie Grahn, Ann Normark, Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr">
@@ -15153,7 +15153,7 @@
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn, Cecilia Goldkuhl, Ann Normark</t>
+          <t>Linda-Marie Grahn, Ann Normark, Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr">

--- a/artfynd/Gålggåmisvárre artfynd.xlsx
+++ b/artfynd/Gålggåmisvárre artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135294829</v>
       </c>
       <c r="B2" t="n">
-        <v>93339</v>
+        <v>93341</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>135301776</v>
       </c>
       <c r="B3" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1509,7 +1509,7 @@
         <v>135294841</v>
       </c>
       <c r="B9" t="n">
-        <v>98142</v>
+        <v>98144</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -2191,7 +2191,7 @@
         <v>135295377</v>
       </c>
       <c r="B15" t="n">
-        <v>92294</v>
+        <v>92296</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2311,7 +2311,7 @@
         <v>135294352</v>
       </c>
       <c r="B16" t="n">
-        <v>92443</v>
+        <v>92445</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -5122,7 +5122,7 @@
         <v>135294361</v>
       </c>
       <c r="B40" t="n">
-        <v>92227</v>
+        <v>92229</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5254,7 +5254,7 @@
         <v>135295390</v>
       </c>
       <c r="B41" t="n">
-        <v>92227</v>
+        <v>92229</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5370,7 +5370,7 @@
         <v>135298393</v>
       </c>
       <c r="B42" t="n">
-        <v>92227</v>
+        <v>92229</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5482,7 +5482,7 @@
         <v>135298394</v>
       </c>
       <c r="B43" t="n">
-        <v>92227</v>
+        <v>92229</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5594,7 +5594,7 @@
         <v>135298401</v>
       </c>
       <c r="B44" t="n">
-        <v>92227</v>
+        <v>92229</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5706,7 +5706,7 @@
         <v>135300576</v>
       </c>
       <c r="B45" t="n">
-        <v>92227</v>
+        <v>92229</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6026,7 +6026,7 @@
         <v>135294851</v>
       </c>
       <c r="B48" t="n">
-        <v>91069</v>
+        <v>91071</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6244,7 +6244,7 @@
         <v>135294365</v>
       </c>
       <c r="B50" t="n">
-        <v>92101</v>
+        <v>92103</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6356,7 +6356,7 @@
         <v>135300496</v>
       </c>
       <c r="B51" t="n">
-        <v>92101</v>
+        <v>92103</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6472,7 +6472,7 @@
         <v>135301730</v>
       </c>
       <c r="B52" t="n">
-        <v>92101</v>
+        <v>92103</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6588,7 +6588,7 @@
         <v>135294359</v>
       </c>
       <c r="B53" t="n">
-        <v>91970</v>
+        <v>91972</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6700,7 +6700,7 @@
         <v>135294363</v>
       </c>
       <c r="B54" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6812,7 +6812,7 @@
         <v>135294852</v>
       </c>
       <c r="B55" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6928,7 +6928,7 @@
         <v>135301781</v>
       </c>
       <c r="B56" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7151,7 +7151,7 @@
         <v>135301740</v>
       </c>
       <c r="B58" t="n">
-        <v>93349</v>
+        <v>93351</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7267,7 +7267,7 @@
         <v>135294351</v>
       </c>
       <c r="B59" t="n">
-        <v>92011</v>
+        <v>92013</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7414,7 +7414,7 @@
         <v>135300495</v>
       </c>
       <c r="B60" t="n">
-        <v>92011</v>
+        <v>92013</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7530,7 +7530,7 @@
         <v>135301732</v>
       </c>
       <c r="B61" t="n">
-        <v>92011</v>
+        <v>92013</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7646,7 +7646,7 @@
         <v>135301797</v>
       </c>
       <c r="B62" t="n">
-        <v>92011</v>
+        <v>92013</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -11710,7 +11710,7 @@
         <v>135294357</v>
       </c>
       <c r="B97" t="n">
-        <v>98142</v>
+        <v>98144</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11822,7 +11822,7 @@
         <v>135294781</v>
       </c>
       <c r="B98" t="n">
-        <v>98142</v>
+        <v>98144</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11938,7 +11938,7 @@
         <v>135294843</v>
       </c>
       <c r="B99" t="n">
-        <v>98142</v>
+        <v>98144</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -12054,7 +12054,7 @@
         <v>135295389</v>
       </c>
       <c r="B100" t="n">
-        <v>98142</v>
+        <v>98144</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -12175,7 +12175,7 @@
         <v>135300497</v>
       </c>
       <c r="B101" t="n">
-        <v>98142</v>
+        <v>98144</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -12291,7 +12291,7 @@
         <v>135301728</v>
       </c>
       <c r="B102" t="n">
-        <v>98136</v>
+        <v>98138</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12407,7 +12407,7 @@
         <v>135301791</v>
       </c>
       <c r="B103" t="n">
-        <v>98136</v>
+        <v>98138</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -15404,7 +15404,7 @@
         <v>135295442</v>
       </c>
       <c r="B129" t="n">
-        <v>93366</v>
+        <v>93368</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -15524,7 +15524,7 @@
         <v>135301801</v>
       </c>
       <c r="B130" t="n">
-        <v>93366</v>
+        <v>93368</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15636,7 +15636,7 @@
         <v>135300502</v>
       </c>
       <c r="B131" t="n">
-        <v>92294</v>
+        <v>92296</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -18844,7 +18844,7 @@
         <v>135294811</v>
       </c>
       <c r="B159" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -19411,7 +19411,7 @@
         <v>135298436</v>
       </c>
       <c r="B164" t="n">
-        <v>92227</v>
+        <v>92229</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -19527,7 +19527,7 @@
         <v>135298437</v>
       </c>
       <c r="B165" t="n">
-        <v>92227</v>
+        <v>92229</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -19643,7 +19643,7 @@
         <v>135300514</v>
       </c>
       <c r="B166" t="n">
-        <v>92227</v>
+        <v>92229</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -19759,7 +19759,7 @@
         <v>135300540</v>
       </c>
       <c r="B167" t="n">
-        <v>92227</v>
+        <v>92229</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -19875,7 +19875,7 @@
         <v>135300566</v>
       </c>
       <c r="B168" t="n">
-        <v>92227</v>
+        <v>92229</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -20297,7 +20297,7 @@
         <v>135300513</v>
       </c>
       <c r="B172" t="n">
-        <v>92101</v>
+        <v>92103</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -20413,7 +20413,7 @@
         <v>135300516</v>
       </c>
       <c r="B173" t="n">
-        <v>92101</v>
+        <v>92103</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -20529,7 +20529,7 @@
         <v>135300519</v>
       </c>
       <c r="B174" t="n">
-        <v>92101</v>
+        <v>92103</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -20747,7 +20747,7 @@
         <v>135300542</v>
       </c>
       <c r="B176" t="n">
-        <v>91970</v>
+        <v>91972</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -20863,7 +20863,7 @@
         <v>135294839</v>
       </c>
       <c r="B177" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -20979,7 +20979,7 @@
         <v>135298447</v>
       </c>
       <c r="B178" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -21095,7 +21095,7 @@
         <v>135301769</v>
       </c>
       <c r="B179" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -30238,7 +30238,7 @@
         <v>135301756</v>
       </c>
       <c r="B260" t="n">
-        <v>111242</v>
+        <v>111244</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -30354,7 +30354,7 @@
         <v>135294816</v>
       </c>
       <c r="B261" t="n">
-        <v>106396</v>
+        <v>106398</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -30470,7 +30470,7 @@
         <v>135301744</v>
       </c>
       <c r="B262" t="n">
-        <v>106396</v>
+        <v>106398</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -30586,7 +30586,7 @@
         <v>135294825</v>
       </c>
       <c r="B263" t="n">
-        <v>98142</v>
+        <v>98144</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -30702,7 +30702,7 @@
         <v>135301741</v>
       </c>
       <c r="B264" t="n">
-        <v>98142</v>
+        <v>98144</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -30818,7 +30818,7 @@
         <v>135301757</v>
       </c>
       <c r="B265" t="n">
-        <v>98142</v>
+        <v>98144</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -30934,7 +30934,7 @@
         <v>135301766</v>
       </c>
       <c r="B266" t="n">
-        <v>98142</v>
+        <v>98144</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -31050,7 +31050,7 @@
         <v>135301770</v>
       </c>
       <c r="B267" t="n">
-        <v>98142</v>
+        <v>98144</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -31166,7 +31166,7 @@
         <v>135301790</v>
       </c>
       <c r="B268" t="n">
-        <v>98142</v>
+        <v>98144</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -31282,7 +31282,7 @@
         <v>135298442</v>
       </c>
       <c r="B269" t="n">
-        <v>98136</v>
+        <v>98138</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -31398,7 +31398,7 @@
         <v>135301747</v>
       </c>
       <c r="B270" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -31514,7 +31514,7 @@
         <v>135301759</v>
       </c>
       <c r="B271" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -31630,7 +31630,7 @@
         <v>135295146</v>
       </c>
       <c r="B272" t="n">
-        <v>100886</v>
+        <v>100888</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>

--- a/artfynd/Gålggåmisvárre artfynd.xlsx
+++ b/artfynd/Gålggåmisvárre artfynd.xlsx
@@ -15404,7 +15404,7 @@
         <v>135295442</v>
       </c>
       <c r="B129" t="n">
-        <v>93368</v>
+        <v>93383</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
